--- a/data/pedigree.xlsx
+++ b/data/pedigree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe-my.sharepoint.com/personal/birgit_deboutte_ugent_be/Documents/Ontwerp Breeding Program R/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{9741D925-DF7A-C544-A3A6-BA12A6F39DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0B82CF-AAC6-7842-9C47-344A75BD5B93}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{D39D626F-8E55-234E-9590-B9BAE593D32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB907B40-665B-644A-A7D6-B28919E580C4}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1160" windowWidth="27640" windowHeight="16480" xr2:uid="{D8B29699-6A0E-D947-977F-F944DBBD9FB9}"/>
+    <workbookView xWindow="63800" yWindow="-13800" windowWidth="34400" windowHeight="28200" xr2:uid="{0635F1F8-11C3-8641-8FB2-C4F0467B12F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Ped_anon" sheetId="1" r:id="rId1"/>
@@ -3960,7 +3960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4F7C9C-A905-3644-B001-0D3C6E56384D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F6642D-0EA3-C343-87CF-2C260E58D1E9}">
   <dimension ref="A1:D852"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
